--- a/output/pdf_financials_xlsx/LOBE.xlsx
+++ b/output/pdf_financials_xlsx/LOBE.xlsx
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>5.937852</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>6.371728</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>6.712183</v>
       </c>
     </row>
     <row r="93">
@@ -3090,7 +3090,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3486,7 +3490,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>5.937852</v>
       </c>

--- a/output/pdf_financials_xlsx/LOBE.xlsx
+++ b/output/pdf_financials_xlsx/LOBE.xlsx
@@ -619,7 +619,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.018645</v>
       </c>
     </row>
     <row r="13">
@@ -871,7 +871,7 @@
         <v>-4.453727</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.861611</v>
+        <v>-4.880256</v>
       </c>
     </row>
     <row r="28">
@@ -903,7 +903,7 @@
         <v>-4.453727</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.861611</v>
+        <v>-4.880256</v>
       </c>
     </row>
     <row r="30">
@@ -972,13 +972,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.14029</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.237772</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>5.854118</v>
       </c>
     </row>
     <row r="35">
@@ -1004,13 +1004,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.14029</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.237772</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.686688</v>
+        <v>7.540806</v>
       </c>
     </row>
     <row r="37">
@@ -1196,13 +1196,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.287461</v>
+        <v>0.147171</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.258076</v>
+        <v>2.020304</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.691338</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">

--- a/output/pdf_financials_xlsx/LOBE.xlsx
+++ b/output/pdf_financials_xlsx/LOBE.xlsx
@@ -539,7 +539,7 @@
         <v>1.0392</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.484983</v>
+        <v>2.136496</v>
       </c>
     </row>
     <row r="8">
@@ -587,7 +587,7 @@
         <v>1.0392</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.484983</v>
+        <v>2.136496</v>
       </c>
     </row>
     <row r="11">
@@ -2195,13 +2195,13 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.02076</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.09599299999999999</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.323817</v>
       </c>
     </row>
     <row r="111">
@@ -3756,7 +3756,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -5095,7 +5099,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E78" s="5" t="n">
         <v>0.02076</v>
       </c>
@@ -5430,7 +5438,11 @@
           <t>Units issued - private placement</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E89" s="5" t="n">
         <v>0.6765</v>
       </c>
@@ -6663,7 +6675,11 @@
           <t>Directors fees 13</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -6675,7 +6691,7 @@
         </is>
       </c>
       <c r="G128" s="5" t="n">
-        <v>-0.651513</v>
+        <v>0.651513</v>
       </c>
     </row>
     <row r="129">
